--- a/Scrum_Report_Team 4..(5) (1).xlsx
+++ b/Scrum_Report_Team 4..(5) (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\307367\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76D3186-0393-4490-AE9C-FE527961502B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C7E203-4F3E-4544-B800-F7235B639793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team_Mapping" sheetId="1" r:id="rId1"/>
@@ -947,7 +947,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -998,13 +998,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -1567,7 +1564,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.7265625" customWidth="1"/>
@@ -1800,104 +1797,98 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="A14" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="26">
+        <v>46107</v>
+      </c>
+      <c r="D14" s="26">
+        <v>46107</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="C15" s="27">
-        <v>46107</v>
-      </c>
-      <c r="D15" s="27">
-        <v>46107</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>200</v>
+      <c r="A15" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" s="26">
+        <v>46108</v>
+      </c>
+      <c r="D15" s="26">
+        <v>46108</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C16" s="27">
-        <v>46108</v>
-      </c>
-      <c r="D16" s="27">
-        <v>46108</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>203</v>
+      <c r="A16" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="C16" s="26">
+        <v>46109</v>
+      </c>
+      <c r="D16" s="26">
+        <v>46109</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="C17" s="27">
-        <v>46109</v>
-      </c>
-      <c r="D17" s="27">
-        <v>46109</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>206</v>
+      <c r="A17" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="C17" s="28">
+        <v>46111</v>
+      </c>
+      <c r="D17" s="28">
+        <v>46111</v>
+      </c>
+      <c r="E17" s="29" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="C18" s="29">
-        <v>46111</v>
-      </c>
-      <c r="D18" s="29">
-        <v>46111</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>209</v>
+      <c r="A18" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="C18" s="28">
+        <v>46112</v>
+      </c>
+      <c r="D18" s="28">
+        <v>46113</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>211</v>
-      </c>
-      <c r="C19" s="29">
-        <v>46112</v>
-      </c>
-      <c r="D19" s="29">
-        <v>46113</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-    </row>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="23" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -1977,7 +1968,6 @@
     <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -3998,191 +3988,191 @@
     </row>
     <row r="85" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="86" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="33" t="s">
+      <c r="A86" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="B86" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" s="33" t="s">
+      <c r="B86" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="30" t="s">
         <v>238</v>
       </c>
-      <c r="D86" s="33" t="s">
+      <c r="D86" s="30" t="s">
         <v>200</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F86" s="31">
-        <v>7</v>
-      </c>
-      <c r="G86" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H86" s="32" t="s">
+      <c r="F86" s="25">
+        <v>7</v>
+      </c>
+      <c r="G86" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H86" s="22" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="33" t="s">
+      <c r="A87" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="B87" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87" s="33" t="s">
+      <c r="B87" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="D87" s="33" t="s">
+      <c r="D87" s="30" t="s">
         <v>200</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F87" s="31">
-        <v>7</v>
-      </c>
-      <c r="G87" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H87" s="32" t="s">
+      <c r="F87" s="25">
+        <v>7</v>
+      </c>
+      <c r="G87" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H87" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="33" t="s">
+      <c r="A88" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="B88" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C88" s="33" t="s">
+      <c r="B88" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="D88" s="33" t="s">
+      <c r="D88" s="30" t="s">
         <v>200</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F88" s="31">
-        <v>7</v>
-      </c>
-      <c r="G88" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H88" s="32" t="s">
+      <c r="F88" s="25">
+        <v>7</v>
+      </c>
+      <c r="G88" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H88" s="22" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="33" t="s">
+      <c r="A89" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="B89" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C89" s="33" t="s">
+      <c r="B89" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="D89" s="33" t="s">
+      <c r="D89" s="30" t="s">
         <v>200</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F89" s="31">
-        <v>7</v>
-      </c>
-      <c r="G89" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H89" s="32" t="s">
+      <c r="F89" s="25">
+        <v>7</v>
+      </c>
+      <c r="G89" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H89" s="22" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="33" t="s">
+      <c r="A90" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="B90" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C90" s="33" t="s">
+      <c r="B90" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="D90" s="33" t="s">
+      <c r="D90" s="30" t="s">
         <v>200</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F90" s="31">
-        <v>7</v>
-      </c>
-      <c r="G90" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H90" s="32" t="s">
+      <c r="F90" s="25">
+        <v>7</v>
+      </c>
+      <c r="G90" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H90" s="22" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="33" t="s">
+      <c r="A91" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="B91" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C91" s="33" t="s">
+      <c r="B91" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="D91" s="33" t="s">
+      <c r="D91" s="30" t="s">
         <v>200</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F91" s="31">
-        <v>7</v>
-      </c>
-      <c r="G91" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H91" s="32" t="s">
+      <c r="F91" s="25">
+        <v>7</v>
+      </c>
+      <c r="G91" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H91" s="22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="31"/>
-      <c r="B92" s="31"/>
-      <c r="C92" s="31"/>
-      <c r="D92" s="31"/>
-      <c r="E92" s="31"/>
-      <c r="F92" s="31"/>
-      <c r="G92" s="31"/>
-      <c r="H92" s="31"/>
+      <c r="A92" s="25"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="25"/>
+      <c r="D92" s="25"/>
+      <c r="E92" s="25"/>
+      <c r="F92" s="25"/>
+      <c r="G92" s="25"/>
+      <c r="H92" s="25"/>
     </row>
     <row r="93" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="33" t="s">
+      <c r="A93" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="B93" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C93" s="33" t="s">
+      <c r="B93" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="D93" s="33" t="s">
+      <c r="D93" s="30" t="s">
         <v>203</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F93" s="31">
-        <v>7</v>
-      </c>
-      <c r="G93" s="33" t="s">
+      <c r="F93" s="25">
+        <v>7</v>
+      </c>
+      <c r="G93" s="30" t="s">
         <v>57</v>
       </c>
       <c r="H93" s="2" t="s">
@@ -4190,25 +4180,25 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="33" t="s">
+      <c r="A94" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="B94" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C94" s="33" t="s">
+      <c r="B94" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="D94" s="33" t="s">
+      <c r="D94" s="30" t="s">
         <v>203</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F94" s="31">
-        <v>7</v>
-      </c>
-      <c r="G94" s="33" t="s">
+      <c r="F94" s="25">
+        <v>7</v>
+      </c>
+      <c r="G94" s="30" t="s">
         <v>57</v>
       </c>
       <c r="H94" s="2" t="s">
@@ -4216,25 +4206,25 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="33" t="s">
+      <c r="A95" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="B95" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C95" s="33" t="s">
+      <c r="B95" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="D95" s="33" t="s">
+      <c r="D95" s="30" t="s">
         <v>203</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F95" s="31">
-        <v>7</v>
-      </c>
-      <c r="G95" s="33" t="s">
+      <c r="F95" s="25">
+        <v>7</v>
+      </c>
+      <c r="G95" s="30" t="s">
         <v>57</v>
       </c>
       <c r="H95" s="2" t="s">
@@ -4242,25 +4232,25 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="33" t="s">
+      <c r="A96" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="B96" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C96" s="33" t="s">
+      <c r="B96" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="D96" s="33" t="s">
+      <c r="D96" s="30" t="s">
         <v>203</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F96" s="31">
-        <v>7</v>
-      </c>
-      <c r="G96" s="33" t="s">
+      <c r="F96" s="25">
+        <v>7</v>
+      </c>
+      <c r="G96" s="30" t="s">
         <v>57</v>
       </c>
       <c r="H96" s="2" t="s">
@@ -4268,25 +4258,25 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="33" t="s">
+      <c r="A97" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="B97" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C97" s="33" t="s">
+      <c r="B97" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="D97" s="33" t="s">
+      <c r="D97" s="30" t="s">
         <v>203</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F97" s="31">
-        <v>7</v>
-      </c>
-      <c r="G97" s="33" t="s">
+      <c r="F97" s="25">
+        <v>7</v>
+      </c>
+      <c r="G97" s="30" t="s">
         <v>57</v>
       </c>
       <c r="H97" s="2" t="s">
@@ -4294,25 +4284,25 @@
       </c>
     </row>
     <row r="98" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="33" t="s">
+      <c r="A98" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="B98" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C98" s="33" t="s">
+      <c r="B98" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="D98" s="33" t="s">
+      <c r="D98" s="30" t="s">
         <v>203</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F98" s="31">
-        <v>7</v>
-      </c>
-      <c r="G98" s="33" t="s">
+      <c r="F98" s="25">
+        <v>7</v>
+      </c>
+      <c r="G98" s="30" t="s">
         <v>57</v>
       </c>
       <c r="H98" s="2" t="s">
@@ -4320,35 +4310,35 @@
       </c>
     </row>
     <row r="99" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="31"/>
-      <c r="B99" s="33"/>
-      <c r="C99" s="31"/>
-      <c r="D99" s="31"/>
-      <c r="E99" s="31"/>
-      <c r="F99" s="31"/>
-      <c r="G99" s="31"/>
-      <c r="H99" s="32"/>
+      <c r="A99" s="25"/>
+      <c r="B99" s="30"/>
+      <c r="C99" s="25"/>
+      <c r="D99" s="25"/>
+      <c r="E99" s="25"/>
+      <c r="F99" s="25"/>
+      <c r="G99" s="25"/>
+      <c r="H99" s="22"/>
     </row>
     <row r="100" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="33" t="s">
+      <c r="A100" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="B100" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C100" s="33" t="s">
+      <c r="B100" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="D100" s="33" t="s">
+      <c r="D100" s="30" t="s">
         <v>206</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F100" s="31">
-        <v>7</v>
-      </c>
-      <c r="G100" s="33" t="s">
+      <c r="F100" s="25">
+        <v>7</v>
+      </c>
+      <c r="G100" s="30" t="s">
         <v>57</v>
       </c>
       <c r="H100" s="2" t="s">
@@ -4356,25 +4346,25 @@
       </c>
     </row>
     <row r="101" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="33" t="s">
+      <c r="A101" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="B101" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C101" s="33" t="s">
+      <c r="B101" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="D101" s="33" t="s">
+      <c r="D101" s="30" t="s">
         <v>206</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F101" s="31">
-        <v>7</v>
-      </c>
-      <c r="G101" s="33" t="s">
+      <c r="F101" s="25">
+        <v>7</v>
+      </c>
+      <c r="G101" s="30" t="s">
         <v>57</v>
       </c>
       <c r="H101" s="2" t="s">
@@ -4382,25 +4372,25 @@
       </c>
     </row>
     <row r="102" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="33" t="s">
+      <c r="A102" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="B102" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C102" s="33" t="s">
+      <c r="B102" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="D102" s="33" t="s">
+      <c r="D102" s="30" t="s">
         <v>206</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F102" s="31">
-        <v>7</v>
-      </c>
-      <c r="G102" s="33" t="s">
+      <c r="F102" s="25">
+        <v>7</v>
+      </c>
+      <c r="G102" s="30" t="s">
         <v>57</v>
       </c>
       <c r="H102" s="2" t="s">
@@ -4408,25 +4398,25 @@
       </c>
     </row>
     <row r="103" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="33" t="s">
+      <c r="A103" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="B103" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C103" s="33" t="s">
+      <c r="B103" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="30" t="s">
         <v>223</v>
       </c>
-      <c r="D103" s="33" t="s">
+      <c r="D103" s="30" t="s">
         <v>206</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F103" s="31">
-        <v>7</v>
-      </c>
-      <c r="G103" s="33" t="s">
+      <c r="F103" s="25">
+        <v>7</v>
+      </c>
+      <c r="G103" s="30" t="s">
         <v>57</v>
       </c>
       <c r="H103" s="2" t="s">
@@ -4434,25 +4424,25 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="33" t="s">
+      <c r="A104" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="B104" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C104" s="33" t="s">
+      <c r="B104" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="30" t="s">
         <v>224</v>
       </c>
-      <c r="D104" s="33" t="s">
+      <c r="D104" s="30" t="s">
         <v>206</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F104" s="31">
-        <v>7</v>
-      </c>
-      <c r="G104" s="33" t="s">
+      <c r="F104" s="25">
+        <v>7</v>
+      </c>
+      <c r="G104" s="30" t="s">
         <v>57</v>
       </c>
       <c r="H104" s="2" t="s">
@@ -4460,25 +4450,25 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="33" t="s">
+      <c r="A105" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="B105" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C105" s="33" t="s">
+      <c r="B105" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="30" t="s">
         <v>225</v>
       </c>
-      <c r="D105" s="33" t="s">
+      <c r="D105" s="30" t="s">
         <v>206</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F105" s="31">
-        <v>7</v>
-      </c>
-      <c r="G105" s="33" t="s">
+      <c r="F105" s="25">
+        <v>7</v>
+      </c>
+      <c r="G105" s="30" t="s">
         <v>57</v>
       </c>
       <c r="H105" s="2" t="s">
@@ -4486,334 +4476,334 @@
       </c>
     </row>
     <row r="106" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="31"/>
-      <c r="B106" s="33"/>
-      <c r="C106" s="31"/>
-      <c r="D106" s="31"/>
-      <c r="E106" s="31"/>
-      <c r="F106" s="31"/>
-      <c r="G106" s="31"/>
-      <c r="H106" s="31"/>
+      <c r="A106" s="25"/>
+      <c r="B106" s="30"/>
+      <c r="C106" s="25"/>
+      <c r="D106" s="25"/>
+      <c r="E106" s="25"/>
+      <c r="F106" s="25"/>
+      <c r="G106" s="25"/>
+      <c r="H106" s="25"/>
     </row>
     <row r="107" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="33" t="s">
+      <c r="A107" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="B107" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C107" s="33" t="s">
+      <c r="B107" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="D107" s="33" t="s">
+      <c r="D107" s="30" t="s">
         <v>209</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F107" s="31">
-        <v>7</v>
-      </c>
-      <c r="G107" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H107" s="32" t="s">
+      <c r="F107" s="25">
+        <v>7</v>
+      </c>
+      <c r="G107" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H107" s="22" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="108" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="33" t="s">
+      <c r="A108" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="B108" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C108" s="33" t="s">
+      <c r="B108" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="D108" s="33" t="s">
+      <c r="D108" s="30" t="s">
         <v>209</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F108" s="31">
-        <v>7</v>
-      </c>
-      <c r="G108" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H108" s="32" t="s">
+      <c r="F108" s="25">
+        <v>7</v>
+      </c>
+      <c r="G108" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H108" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="33" t="s">
+      <c r="A109" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="B109" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C109" s="33" t="s">
+      <c r="B109" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C109" s="30" t="s">
         <v>228</v>
       </c>
-      <c r="D109" s="33" t="s">
+      <c r="D109" s="30" t="s">
         <v>209</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F109" s="31">
-        <v>7</v>
-      </c>
-      <c r="G109" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H109" s="32" t="s">
+      <c r="F109" s="25">
+        <v>7</v>
+      </c>
+      <c r="G109" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H109" s="22" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="33" t="s">
+      <c r="A110" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="B110" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C110" s="33" t="s">
+      <c r="B110" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C110" s="30" t="s">
         <v>229</v>
       </c>
-      <c r="D110" s="33" t="s">
+      <c r="D110" s="30" t="s">
         <v>209</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F110" s="31">
-        <v>7</v>
-      </c>
-      <c r="G110" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H110" s="32" t="s">
+      <c r="F110" s="25">
+        <v>7</v>
+      </c>
+      <c r="G110" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H110" s="22" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="33" t="s">
+      <c r="A111" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="B111" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C111" s="33" t="s">
+      <c r="B111" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" s="30" t="s">
         <v>230</v>
       </c>
-      <c r="D111" s="33" t="s">
+      <c r="D111" s="30" t="s">
         <v>209</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F111" s="31">
-        <v>7</v>
-      </c>
-      <c r="G111" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H111" s="32" t="s">
+      <c r="F111" s="25">
+        <v>7</v>
+      </c>
+      <c r="G111" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H111" s="22" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="33" t="s">
+      <c r="A112" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="B112" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C112" s="33" t="s">
+      <c r="B112" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="D112" s="33" t="s">
+      <c r="D112" s="30" t="s">
         <v>209</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F112" s="31">
-        <v>7</v>
-      </c>
-      <c r="G112" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H112" s="32" t="s">
+      <c r="F112" s="25">
+        <v>7</v>
+      </c>
+      <c r="G112" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H112" s="22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="31"/>
-      <c r="B113" s="33"/>
-      <c r="C113" s="31"/>
-      <c r="D113" s="31"/>
-      <c r="E113" s="31"/>
-      <c r="F113" s="31"/>
-      <c r="G113" s="31"/>
-      <c r="H113" s="31"/>
+      <c r="A113" s="25"/>
+      <c r="B113" s="30"/>
+      <c r="C113" s="25"/>
+      <c r="D113" s="25"/>
+      <c r="E113" s="25"/>
+      <c r="F113" s="25"/>
+      <c r="G113" s="25"/>
+      <c r="H113" s="25"/>
     </row>
     <row r="114" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="33" t="s">
+      <c r="A114" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="B114" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C114" s="33" t="s">
+      <c r="B114" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="D114" s="33" t="s">
+      <c r="D114" s="30" t="s">
         <v>212</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F114" s="31">
-        <v>7</v>
-      </c>
-      <c r="G114" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H114" s="32" t="s">
+      <c r="F114" s="25">
+        <v>7</v>
+      </c>
+      <c r="G114" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H114" s="22" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="33" t="s">
+      <c r="A115" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="B115" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C115" s="33" t="s">
+      <c r="B115" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C115" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="D115" s="33" t="s">
+      <c r="D115" s="30" t="s">
         <v>212</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F115" s="31">
-        <v>7</v>
-      </c>
-      <c r="G115" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H115" s="32" t="s">
+      <c r="F115" s="25">
+        <v>7</v>
+      </c>
+      <c r="G115" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H115" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="33" t="s">
+      <c r="A116" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="B116" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C116" s="33" t="s">
+      <c r="B116" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="D116" s="33" t="s">
+      <c r="D116" s="30" t="s">
         <v>212</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F116" s="31">
-        <v>7</v>
-      </c>
-      <c r="G116" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H116" s="32" t="s">
+      <c r="F116" s="25">
+        <v>7</v>
+      </c>
+      <c r="G116" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H116" s="22" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="33" t="s">
+      <c r="A117" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="B117" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C117" s="33" t="s">
+      <c r="B117" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="D117" s="33" t="s">
+      <c r="D117" s="30" t="s">
         <v>212</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F117" s="31">
-        <v>7</v>
-      </c>
-      <c r="G117" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H117" s="32" t="s">
+      <c r="F117" s="25">
+        <v>7</v>
+      </c>
+      <c r="G117" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H117" s="22" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="33" t="s">
+      <c r="A118" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="B118" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C118" s="33" t="s">
+      <c r="B118" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C118" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="D118" s="33" t="s">
+      <c r="D118" s="30" t="s">
         <v>212</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F118" s="31">
-        <v>7</v>
-      </c>
-      <c r="G118" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H118" s="32" t="s">
+      <c r="F118" s="25">
+        <v>7</v>
+      </c>
+      <c r="G118" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H118" s="22" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="33" t="s">
+      <c r="A119" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="B119" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C119" s="33" t="s">
+      <c r="B119" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C119" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="D119" s="33" t="s">
+      <c r="D119" s="30" t="s">
         <v>212</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F119" s="31">
-        <v>7</v>
-      </c>
-      <c r="G119" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="H119" s="32" t="s">
+      <c r="F119" s="25">
+        <v>7</v>
+      </c>
+      <c r="G119" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H119" s="22" t="s">
         <v>15</v>
       </c>
     </row>
